--- a/task177/golden/assistant_share_forecast_mar_apr_2027.xlsx
+++ b/task177/golden/assistant_share_forecast_mar_apr_2027.xlsx
@@ -226,7 +226,7 @@
     <t>2026</t>
   </si>
   <si>
-    <t>A conversation counts once, in the month its first session started, Manitoba time. The test employers registered to our own business number are our own use; the employer widget writes UTC, moved here to Manitoba time.</t>
+    <t>A conversation counts once, in the month its first session started, Manitoba time. The test employers registered to our own business number are our own use; the employer widget writes UTC, moved here to Manitoba time. Riverlot's support desk works in the staff console under accounts registered to Riverlot's business number; those conversations are the vendor's and are not counted.</t>
   </si>
   <si>
     <t>As of</t>
@@ -1260,7 +1260,7 @@
         <v>42</v>
       </c>
       <c r="B2" s="3">
-        <v>930</v>
+        <v>945</v>
       </c>
       <c r="C2" s="3">
         <v>1256</v>
@@ -1271,7 +1271,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>1020</v>
+        <v>1040</v>
       </c>
       <c r="C3" s="3">
         <v>1148</v>
@@ -1282,7 +1282,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="3">
-        <v>1519</v>
+        <v>1555</v>
       </c>
       <c r="C4" s="3">
         <v>1326</v>
@@ -1293,7 +1293,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="3">
-        <v>1656</v>
+        <v>1686</v>
       </c>
       <c r="C5" s="3">
         <v>1171</v>
@@ -1304,7 +1304,7 @@
         <v>46</v>
       </c>
       <c r="B6" s="3">
-        <v>1840</v>
+        <v>1850</v>
       </c>
       <c r="C6" s="3">
         <v>1163</v>
@@ -1315,7 +1315,7 @@
         <v>47</v>
       </c>
       <c r="B7" s="3">
-        <v>1815</v>
+        <v>1852</v>
       </c>
       <c r="C7" s="3">
         <v>1217</v>
@@ -1326,7 +1326,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="3">
-        <v>1621</v>
+        <v>1660</v>
       </c>
       <c r="C8" s="3">
         <v>1332</v>
@@ -1337,7 +1337,7 @@
         <v>49</v>
       </c>
       <c r="B9" s="3">
-        <v>1360</v>
+        <v>1399</v>
       </c>
       <c r="C9" s="3">
         <v>1161</v>
@@ -1348,7 +1348,7 @@
         <v>50</v>
       </c>
       <c r="B10" s="3">
-        <v>1811</v>
+        <v>1838</v>
       </c>
       <c r="C10" s="3">
         <v>1224</v>
@@ -1359,7 +1359,7 @@
         <v>51</v>
       </c>
       <c r="B11" s="3">
-        <v>1772</v>
+        <v>1794</v>
       </c>
       <c r="C11" s="3">
         <v>1208</v>
@@ -1370,7 +1370,7 @@
         <v>52</v>
       </c>
       <c r="B12" s="3">
-        <v>1760</v>
+        <v>1799</v>
       </c>
       <c r="C12" s="3">
         <v>1252</v>
@@ -1381,7 +1381,7 @@
         <v>53</v>
       </c>
       <c r="B13" s="3">
-        <v>1172</v>
+        <v>1203</v>
       </c>
       <c r="C13" s="3">
         <v>1244</v>
@@ -1392,7 +1392,7 @@
         <v>66</v>
       </c>
       <c r="B14" s="10">
-        <v>18276</v>
+        <v>18621</v>
       </c>
       <c r="C14" s="10">
         <v>14702</v>

--- a/task177/golden/assistant_share_forecast_mar_apr_2027.xlsx
+++ b/task177/golden/assistant_share_forecast_mar_apr_2027.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
   <si>
     <t>Ask Prairie Works: share of jobseekers' own contacts, 1 March to 25 April 2027</t>
   </si>
@@ -40,9 +40,6 @@
     <t>Their share in the last eight weeks of 2026 (whole per cent)</t>
   </si>
   <si>
-    <t>Their share during the assistant-first weeks, 4 January to 28 February (whole per cent)</t>
-  </si>
-  <si>
     <t>Inputs</t>
   </si>
   <si>
@@ -226,7 +223,7 @@
     <t>2026</t>
   </si>
   <si>
-    <t>A conversation counts once, in the month its first session started, Manitoba time. The test employers registered to our own business number are our own use; the employer widget writes UTC, moved here to Manitoba time. Riverlot's support desk works in the staff console under accounts registered to Riverlot's business number; those conversations are the vendor's and are not counted.</t>
+    <t>A conversation counts once, in the month its first session started, Manitoba time. The test employers registered to our own business number are our own use; the employer widget writes UTC, moved here to Manitoba time, and closes the sessions open at midnight UTC, carrying each on as a new conversation from the same account, counted here once. Riverlot's support desk works in the staff console under accounts registered to Riverlot's business number; those conversations are the vendor's and are not counted.</t>
   </si>
   <si>
     <t>As of</t>
@@ -655,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE1EE95A-E710-5166-8CC9-5814DF093BE6}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="86.7109375" customWidth="1"/>
@@ -696,17 +693,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>18</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>6</v>
+      </c>
+      <c r="B9" s="4">
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -714,7 +711,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="4">
-        <v>85</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -722,44 +719,44 @@
         <v>8</v>
       </c>
       <c r="B11" s="4">
-        <v>88.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="4">
-        <v>3.3</v>
+      <c r="B12" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" t="s">
         <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
         <v>16</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0.4</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -767,22 +764,14 @@
         <v>17</v>
       </c>
       <c r="B18" s="5">
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="5">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20">
+      <c r="B19">
         <v>40</v>
       </c>
     </row>
@@ -809,36 +798,36 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" s="7">
         <v>-133588.9</v>
@@ -867,7 +856,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="7">
         <v>-135008.3</v>
@@ -896,7 +885,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="7">
         <v>-133681.5</v>
@@ -925,7 +914,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="7">
         <v>-134726.2</v>
@@ -954,7 +943,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="7">
         <v>-133721.7</v>
@@ -983,31 +972,31 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12">
         <v>14</v>
@@ -1021,7 +1010,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13">
         <v>14</v>
@@ -1050,15 +1039,15 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2">
         <v>35</v>
@@ -1066,7 +1055,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3">
         <v>24</v>
@@ -1074,7 +1063,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4">
         <v>19</v>
@@ -1082,7 +1071,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>16</v>
@@ -1090,7 +1079,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6">
         <v>15</v>
@@ -1098,7 +1087,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7">
         <v>14</v>
@@ -1106,7 +1095,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8">
         <v>15</v>
@@ -1114,7 +1103,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9">
         <v>14</v>
@@ -1122,7 +1111,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10">
         <v>15</v>
@@ -1130,7 +1119,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11">
         <v>14</v>
@@ -1138,7 +1127,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12">
         <v>14</v>
@@ -1146,7 +1135,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13">
         <v>14</v>
@@ -1154,18 +1143,18 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16">
         <v>64.7</v>
@@ -1176,7 +1165,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17">
         <v>26.8</v>
@@ -1187,7 +1176,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18">
         <v>11.7</v>
@@ -1198,7 +1187,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19">
         <v>9.1</v>
@@ -1209,7 +1198,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20">
         <v>6.6</v>
@@ -1220,7 +1209,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B21">
         <v>28.7</v>
@@ -1246,18 +1235,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3">
         <v>945</v>
@@ -1268,7 +1257,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3">
         <v>1040</v>
@@ -1279,7 +1268,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3">
         <v>1555</v>
@@ -1290,7 +1279,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3">
         <v>1686</v>
@@ -1301,7 +1290,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="3">
         <v>1850</v>
@@ -1312,7 +1301,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3">
         <v>1852</v>
@@ -1323,7 +1312,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3">
         <v>1660</v>
@@ -1334,7 +1323,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3">
         <v>1399</v>
@@ -1345,7 +1334,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3">
         <v>1838</v>
@@ -1356,7 +1345,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3">
         <v>1794</v>
@@ -1367,7 +1356,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="3">
         <v>1799</v>
@@ -1378,7 +1367,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="3">
         <v>1203</v>
@@ -1389,7 +1378,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14" s="10">
         <v>18621</v>
@@ -1400,7 +1389,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1419,66 +1408,66 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>68</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>72</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>76</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>78</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>80</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/task177/golden/assistant_share_forecast_mar_apr_2027.xlsx
+++ b/task177/golden/assistant_share_forecast_mar_apr_2027.xlsx
@@ -31,7 +31,7 @@
     <t>Digital Channels, prepared 5 January 2027 for the March and April usage tier</t>
   </si>
   <si>
-    <t>Forecast share started in Ask Prairie Works (whole per cent)</t>
+    <t>Forecast share started in Ask Prairie Works (nearest 5 per cent)</t>
   </si>
   <si>
     <t>Jobseekers on the register on 3 January 2027</t>
@@ -79,7 +79,7 @@
     <t>Learning rate, overflow transfers</t>
   </si>
   <si>
-    <t>One learning rate for every contact would give (whole per cent)</t>
+    <t>One learning rate for every contact would give (nearest 5 per cent)</t>
   </si>
   <si>
     <t>Model</t>
@@ -106,7 +106,7 @@
     <t>Pull to last choice</t>
   </si>
   <si>
-    <t>Forecast share (whole per cent)</t>
+    <t>Forecast share (nearest 5 per cent)</t>
   </si>
   <si>
     <t>Separate rate for overflow transfers (used)</t>
@@ -265,7 +265,7 @@
     <t>Rounding</t>
   </si>
   <si>
-    <t>Shares to the whole per cent, rounded once from the unrounded forecast; counts whole.</t>
+    <t>The forecast shares to the nearest 5 per cent, rounded once from the unrounded forecast; the 2026 record's shares to the whole per cent; counts whole.</t>
   </si>
   <si>
     <t>Sources</t>
@@ -674,7 +674,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -851,7 +851,7 @@
         <v>0.31</v>
       </c>
       <c r="I2" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -967,7 +967,7 @@
         <v>0.28</v>
       </c>
       <c r="I6" s="8">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">

--- a/task177/golden/assistant_share_forecast_mar_apr_2027.xlsx
+++ b/task177/golden/assistant_share_forecast_mar_apr_2027.xlsx
@@ -259,7 +259,7 @@
     <t>Release 4.0</t>
   </si>
   <si>
-    <t>Resolving 2,041 of the acceptance test's 2,400 conversations.</t>
+    <t>Resolving 2,003 of the acceptance test's 2,400 conversations, in the app, on the web and on the voice service (rollout plan 1.3).</t>
   </si>
   <si>
     <t>Rounding</t>
@@ -703,7 +703,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="4">
-        <v>85</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -967,7 +967,7 @@
         <v>0.28</v>
       </c>
       <c r="I6" s="8">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
